--- a/tools/importer/reports/import-residential-tips.report.xlsx
+++ b/tools/importer/reports/import-residential-tips.report.xlsx
@@ -52,10 +52,10 @@
     <t>residential-tips</t>
   </si>
   <si>
-    <t>2026-07-30T13:31:15.734Z</t>
-  </si>
-  <si>
-    <t>Energy Saving Tips | Residential Services | Xcel Energy</t>
+    <t>2026-07-31T03:43:39.130Z</t>
+  </si>
+  <si>
+    <t>Energy Saving Tips | Residential Services | X Energy</t>
   </si>
   <si>
     <t>https://co.my.xcelenergy.com/s/residential/tips</t>
